--- a/artfynd/A 24384-2023 artfynd.xlsx
+++ b/artfynd/A 24384-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24384-2023 artfynd.xlsx
+++ b/artfynd/A 24384-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>113387937</v>
       </c>
       <c r="B2" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,6 +798,323 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131457175</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>666079</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6571192</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131457168</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>666079</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6571192</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131457172</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>666079</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6571192</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24384-2023 artfynd.xlsx
+++ b/artfynd/A 24384-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113387937</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457175</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457168</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,8 +1135,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457172</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>